--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461089.6368282323</v>
+        <v>461090</v>
       </c>
       <c r="R2" t="n">
-        <v>6352091.158429455</v>
+        <v>6352091</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461089.6368282323</v>
+        <v>461090</v>
       </c>
       <c r="R3" t="n">
-        <v>6352091.158429455</v>
+        <v>6352091</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +849,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107046</v>
+        <v>107050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107050</v>
+        <v>107058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107061</v>
+        <v>107066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107066</v>
+        <v>107074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553392</v>
       </c>
       <c r="B2" t="n">
-        <v>107074</v>
+        <v>107084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74857187</v>
       </c>
       <c r="B3" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74553392</v>
+        <v>7157079</v>
       </c>
       <c r="B2" t="n">
-        <v>107084</v>
+        <v>103657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>576</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Skaftslamkrypa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Elatine hexandra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lapierre) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gåeryd, Sm</t>
+          <t>Betad sjöstrand V Gåeryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461090</v>
+        <v>461053</v>
       </c>
       <c r="R2" t="n">
-        <v>6352091</v>
+        <v>6352166</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>1980-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1985-12-31</t>
+          <t>1980-08-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E0c 4725. SOM: Lathraea squamaria. LEG: Thomas Karlsson</t>
+          <t>Spridda bestånd på sandbotten med tunt dylager, på ca 1 dm djup</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,29 +769,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74857187</v>
+        <v>74553392</v>
       </c>
       <c r="B3" t="n">
-        <v>105732</v>
+        <v>107608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,27 +800,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>28 Skärvälla södra gdn 1225 m NV, Sm</t>
+          <t>Gåeryd, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -846,7 +854,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +864,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E0c 4725. SOM: Pyrola chlorantha. LEG: Thomas Karlsson, Lennart Stenberg, Torsten Johansson, Håkan Bengtson, Per-Uno Hagström</t>
+          <t>Smålands flora 2007: KOO: 6E0c 4725. SOM: Lathraea squamaria. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,11 +876,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Frisk skogsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -885,6 +888,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>74857187</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>28 Skärvälla södra gdn 1225 m NV, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>461090</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6352091</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nydala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1985-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E0c 4725. SOM: Pyrola chlorantha. LEG: Thomas Karlsson, Lennart Stenberg, Torsten Johansson, Håkan Bengtson, Per-Uno Hagström</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Frisk skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 29356-2024 artfynd.xlsx
+++ b/artfynd/A 29356-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7157079</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74553392</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,8 +1018,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74857187</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>